--- a/ALS.xlsx
+++ b/ALS.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,19 +425,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -561,9 +547,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>134</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -576,9 +560,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>37.8</v>
-      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -591,9 +573,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>148</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -606,9 +586,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>4.86</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -621,9 +599,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>258</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -675,9 +651,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>0.247</v>
-      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -690,9 +664,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>0.299</v>
-      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -705,9 +677,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>1.14</v>
-      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -733,9 +703,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>316</v>
-      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -748,9 +716,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>27.2</v>
-      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -763,9 +729,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>43.4</v>
-      </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -778,9 +742,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>5</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -793,9 +755,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -808,9 +768,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>134</v>
-      </c>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -823,9 +781,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -838,9 +794,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>6</v>
-      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -853,9 +807,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -868,11 +820,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -885,9 +833,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>2</v>
-      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -900,9 +846,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -915,9 +859,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>5</v>
-      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -930,9 +872,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>43.6</v>
-      </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -945,9 +885,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -960,9 +898,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>4.14</v>
-      </c>
+      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -975,9 +911,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -990,9 +924,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>5</v>
-      </c>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1005,9 +937,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>10</v>
-      </c>
+      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1020,9 +950,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>31.4</v>
-      </c>
+      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1035,11 +963,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1052,11 +976,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1069,9 +989,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1084,9 +1002,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1099,9 +1015,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1114,9 +1028,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1129,9 +1041,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
+      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1144,9 +1054,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>2</v>
-      </c>
+      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1159,11 +1067,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1176,9 +1080,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1191,11 +1093,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1208,9 +1106,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1223,9 +1119,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1238,9 +1132,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1253,9 +1145,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1268,9 +1158,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>0.22</v>
-      </c>
+      <c r="C56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1283,9 +1171,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>0.22</v>
-      </c>
+      <c r="C57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1298,9 +1184,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1313,9 +1197,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1328,9 +1210,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1343,9 +1223,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1358,11 +1236,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1375,9 +1249,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
+      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1390,9 +1262,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
+      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1405,9 +1275,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1420,9 +1288,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>0.28</v>
-      </c>
+      <c r="C66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1435,9 +1301,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1450,11 +1314,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1467,9 +1327,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1482,11 +1340,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1499,9 +1353,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
+      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1514,9 +1366,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>1</v>
-      </c>
+      <c r="C72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1529,11 +1379,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1546,11 +1392,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1563,9 +1405,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1578,9 +1418,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1593,9 +1431,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
+      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1608,9 +1444,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1623,11 +1457,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1640,9 +1470,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1655,9 +1483,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1670,9 +1496,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="C82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1685,9 +1509,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
+      <c r="C83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1700,9 +1522,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1715,9 +1535,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1730,9 +1548,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
+      <c r="C86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1745,9 +1561,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1760,11 +1574,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1777,9 +1587,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1792,9 +1600,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1820,11 +1626,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1850,11 +1652,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
